--- a/data/metadata/Informe-01-010026-A-TC-TM-TP.xlsx
+++ b/data/metadata/Informe-01-010026-A-TC-TM-TP.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://riamlab-my.sharepoint.com/personal/fernandomartinez_gnoss_com/Documents/Proyectos/AOD/Repositorios/local-data-aragopedia/data/metadata/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_8B91B7C394C2120961022FA45D4F80EF9E476F66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{356163E6-B326-4B17-85C4-5A84183E7090}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="765" yWindow="8595" windowWidth="17910" windowHeight="7845" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Informe-01-010026-A-TC-TM-TP" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Informe-01-010026-A-TC-TM-TP" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -20,223 +25,236 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
-  <si>
-    <t xml:space="preserve">Año</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCAA código</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCAA nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comarca código</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comarca nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provincia código</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provincia nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipio código</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipio nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado de la información</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licencias, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licencias, nueva planta, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licencias, nueva planta, con demolición</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licencias, nueva planta, sin demolición</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licencias, rehabilitación, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licencias, rehabilitación, con demolición</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licencias, rehabilitación, sin demolición</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licencias, rehabilitación locales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licencias, demolición</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ccaa-codigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ccaa-nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comarca-codigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comarca-nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">provincia-codigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">provincia-nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">municipio-codigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">municipio-nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estado-de-la-informacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">licencias-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">licencias-nueva-planta-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">licencias-nueva-planta-con-demolicion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">licencias-nueva-planta-sin-demolicion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">licencias-rehabilitacion-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">licencias-rehabilitacion-con-demolicion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">licencias-rehabilitacion-sin-demolicion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">licencias-rehabilitacion-locales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">licencias-demolicion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sdmx-dimension:refPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sdmx-dimension:refArea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaest-dimension:estado-de-la-informacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaest-measure:licencias-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaest-measure:licencias-nueva-planta-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaest-measure:licencias-nueva-planta-con-demolicion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaest-measure:licencias-nueva-planta-sin-demolicion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaest-measure:licencias-rehabilitacion-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaest-measure:licencias-rehabilitacion-con-demolicion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaest-measure:licencias-rehabilitacion-sin-demolicion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaest-measure:licencias-rehabilitacion-locales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaest-measure:licencias-demolicion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xsd:date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URI-Comunidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URI-comarca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URI-Provincia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URI-Municipio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skos:Concept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xsd:int</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
+  <si>
+    <t>Año</t>
+  </si>
+  <si>
+    <t>CCAA código</t>
+  </si>
+  <si>
+    <t>CCAA nombre</t>
+  </si>
+  <si>
+    <t>Comarca código</t>
+  </si>
+  <si>
+    <t>Comarca nombre</t>
+  </si>
+  <si>
+    <t>Provincia código</t>
+  </si>
+  <si>
+    <t>Provincia nombre</t>
+  </si>
+  <si>
+    <t>Municipio código</t>
+  </si>
+  <si>
+    <t>Municipio nombre</t>
+  </si>
+  <si>
+    <t>Estado de la información</t>
+  </si>
+  <si>
+    <t>Licencias, total</t>
+  </si>
+  <si>
+    <t>Licencias, nueva planta, total</t>
+  </si>
+  <si>
+    <t>Licencias, nueva planta, con demolición</t>
+  </si>
+  <si>
+    <t>Licencias, nueva planta, sin demolición</t>
+  </si>
+  <si>
+    <t>Licencias, rehabilitación, total</t>
+  </si>
+  <si>
+    <t>Licencias, rehabilitación, con demolición</t>
+  </si>
+  <si>
+    <t>Licencias, rehabilitación, sin demolición</t>
+  </si>
+  <si>
+    <t>Licencias, rehabilitación locales</t>
+  </si>
+  <si>
+    <t>Licencias, demolición</t>
+  </si>
+  <si>
+    <t>ano</t>
+  </si>
+  <si>
+    <t>ccaa-codigo</t>
+  </si>
+  <si>
+    <t>ccaa-nombre</t>
+  </si>
+  <si>
+    <t>comarca-codigo</t>
+  </si>
+  <si>
+    <t>comarca-nombre</t>
+  </si>
+  <si>
+    <t>provincia-codigo</t>
+  </si>
+  <si>
+    <t>provincia-nombre</t>
+  </si>
+  <si>
+    <t>municipio-codigo</t>
+  </si>
+  <si>
+    <t>municipio-nombre</t>
+  </si>
+  <si>
+    <t>estado-de-la-informacion</t>
+  </si>
+  <si>
+    <t>licencias-total</t>
+  </si>
+  <si>
+    <t>licencias-nueva-planta-total</t>
+  </si>
+  <si>
+    <t>licencias-nueva-planta-con-demolicion</t>
+  </si>
+  <si>
+    <t>licencias-nueva-planta-sin-demolicion</t>
+  </si>
+  <si>
+    <t>licencias-rehabilitacion-total</t>
+  </si>
+  <si>
+    <t>licencias-rehabilitacion-con-demolicion</t>
+  </si>
+  <si>
+    <t>licencias-rehabilitacion-sin-demolicion</t>
+  </si>
+  <si>
+    <t>licencias-rehabilitacion-locales</t>
+  </si>
+  <si>
+    <t>licencias-demolicion</t>
+  </si>
+  <si>
+    <t>sdmx-dimension:refPeriod</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>sdmx-dimension:refArea</t>
+  </si>
+  <si>
+    <t>iaest-dimension:estado-de-la-informacion</t>
+  </si>
+  <si>
+    <t>iaest-measure:licencias-total</t>
+  </si>
+  <si>
+    <t>iaest-measure:licencias-nueva-planta-total</t>
+  </si>
+  <si>
+    <t>iaest-measure:licencias-nueva-planta-con-demolicion</t>
+  </si>
+  <si>
+    <t>iaest-measure:licencias-nueva-planta-sin-demolicion</t>
+  </si>
+  <si>
+    <t>iaest-measure:licencias-rehabilitacion-total</t>
+  </si>
+  <si>
+    <t>iaest-measure:licencias-rehabilitacion-con-demolicion</t>
+  </si>
+  <si>
+    <t>iaest-measure:licencias-rehabilitacion-sin-demolicion</t>
+  </si>
+  <si>
+    <t>iaest-measure:licencias-rehabilitacion-locales</t>
+  </si>
+  <si>
+    <t>iaest-measure:licencias-demolicion</t>
+  </si>
+  <si>
+    <t>dim</t>
+  </si>
+  <si>
+    <t>medida</t>
+  </si>
+  <si>
+    <t>xsd:date</t>
+  </si>
+  <si>
+    <t>URI-Comunidad</t>
+  </si>
+  <si>
+    <t>URI-comarca</t>
+  </si>
+  <si>
+    <t>URI-Provincia</t>
+  </si>
+  <si>
+    <t>URI-Municipio</t>
+  </si>
+  <si>
+    <t>skos:Concept</t>
+  </si>
+  <si>
+    <t>xsd:int</t>
+  </si>
+  <si>
+    <t>Edificios nueva planta, total</t>
+  </si>
+  <si>
+    <t>Superficie nueva planta, total</t>
+  </si>
+  <si>
+    <t>Viviendas nueva planta</t>
+  </si>
+  <si>
+    <t>edificios-nueva-planta-total</t>
+  </si>
+  <si>
+    <t>iaest-measure:edificios-nueva-planta-total</t>
+  </si>
+  <si>
+    <t>superficie-nueva-planta-total</t>
+  </si>
+  <si>
+    <t>iaest-measure:superficie-nueva-planta-total</t>
+  </si>
+  <si>
+    <t>viviendas-nueva-planta</t>
+  </si>
+  <si>
+    <t>iaest-measure:viviendas-nueva-planta</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -248,7 +266,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -256,77 +274,347 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:V5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="47.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="27.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="46.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="19.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="29.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="16" style="0" width="11.52"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="55.140625" customWidth="1"/>
+    <col min="5" max="5" width="34.5703125" customWidth="1"/>
+    <col min="6" max="6" width="36.28515625" customWidth="1"/>
+    <col min="7" max="7" width="47.28515625" customWidth="1"/>
+    <col min="8" max="10" width="27.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" customWidth="1"/>
+    <col min="12" max="12" width="46.42578125" customWidth="1"/>
+    <col min="13" max="13" width="19.140625" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="29.42578125" customWidth="1"/>
+    <col min="16" max="1025" width="11.5703125"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -384,8 +672,17 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -443,8 +740,17 @@
       <c r="S2" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="T2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
@@ -502,8 +808,17 @@
       <c r="S3" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="T3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
@@ -561,8 +876,17 @@
       <c r="S4" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="T4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>53</v>
       </c>
@@ -620,14 +944,18 @@
       <c r="S5" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="T5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>